--- a/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-JDV-J05-SubjectRole-CISIS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="941">
   <si>
     <t>Property</t>
   </si>
@@ -2759,12 +2759,6 @@
   </si>
   <si>
     <t>Attaché de recherche clinique</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
   </si>
   <si>
     <t>365</t>
@@ -3629,7 +3623,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4238,26 +4232,18 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>940</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>941</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
